--- a/reports/source-inventory/信源清单-本地网络标注-2026-08-31.xlsx
+++ b/reports/source-inventory/信源清单-本地网络标注-2026-08-31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ai-news\reports\source-inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1849D6AA-4233-4FE7-B561-DA6FCE7F7B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E368D3-3023-454E-8692-E1A1A95F9EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
